--- a/EMPLOYEE_SALARY_ANALYSIS.xlsx
+++ b/EMPLOYEE_SALARY_ANALYSIS.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9f3280f71f42ce0/Dokumen/Desktop/New folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9f3280f71f42ce0/Dokumen/Desktop/EXCEL_LEARNING/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{028B4F9D-5CE6-4548-8306-B7020E727F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{028B4F9D-5CE6-4548-8306-B7020E727F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC2554D9-F8A5-4193-A39D-6A434CE3C34A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D124A0E7-F699-4039-B1CE-F666AEF1D719}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D124A0E7-F699-4039-B1CE-F666AEF1D719}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DASHBOARD" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$9</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>S.NO</t>
   </si>
@@ -114,13 +115,19 @@
   </si>
   <si>
     <t>RESULT</t>
+  </si>
+  <si>
+    <t>EMPLOYEE SALARY DASHBOARD</t>
+  </si>
+  <si>
+    <t>TOTAL EMPLOYEES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +143,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -145,7 +160,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -153,14 +168,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,4 +759,78 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467A3BE6-9EBD-45ED-881F-F2E70BB7CADC}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A4" s="5">
+        <f>COUNTA(Sheet1!C2:C6)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A7" s="5">
+        <f>SUM(Sheet1!E2:E6)</f>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A10" s="5">
+        <f>AVERAGE(Sheet1!E2:E6)</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A13" s="5">
+        <f>MAX(Sheet1!E2:E6)</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A16" s="5">
+        <f>MIN(Sheet1!E2:E6)</f>
+        <v>25000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/EMPLOYEE_SALARY_ANALYSIS.xlsx
+++ b/EMPLOYEE_SALARY_ANALYSIS.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9f3280f71f42ce0/Dokumen/Desktop/EXCEL_LEARNING/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{028B4F9D-5CE6-4548-8306-B7020E727F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC2554D9-F8A5-4193-A39D-6A434CE3C34A}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{028B4F9D-5CE6-4548-8306-B7020E727F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4A0B4F-A4FB-4925-9813-7ECA8A941F8D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D124A0E7-F699-4039-B1CE-F666AEF1D719}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="DASHBOARD" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="DASHBOARD" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="10" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>S.NO</t>
   </si>
@@ -122,12 +126,24 @@
   <si>
     <t>TOTAL EMPLOYEES</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of NAME</t>
+  </si>
+  <si>
+    <t>SUMMARY</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +162,14 @@
     <font>
       <b/>
       <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -187,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -200,6 +224,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -215,6 +245,2514 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[EMPLOYEE_SALARY_ANALYSIS.xlsx]Sheet2!PivotTable4</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>EMPLOYEES</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> BY DEPARTMENT</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-965A-4705-AFE2-8378A2FE8FE9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-965A-4705-AFE2-8378A2FE8FE9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-965A-4705-AFE2-8378A2FE8FE9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-965A-4705-AFE2-8378A2FE8FE9}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-965A-4705-AFE2-8378A2FE8FE9}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-965A-4705-AFE2-8378A2FE8FE9}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>FINANCE</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-965A-4705-AFE2-8378A2FE8FE9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1">
+          <a:alpha val="97000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13502537182852142"/>
+          <c:y val="0.10226851851851854"/>
+          <c:w val="0.86497462817147852"/>
+          <c:h val="0.72125801983085447"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SALARY</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent6">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$2:$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Priya</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Raja</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sasi</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mani</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Saras</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2A33-470F-A4C7-3A61D60E8EA4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1714418464"/>
+        <c:axId val="1277780464"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1714418464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1277780464"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1277780464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1714418464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="302">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>236220</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73F31094-DB5C-4B97-BA71-97EE573DD303}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>243840</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D6D03F-4783-4C70-A31A-6E18FEBCF72E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="SARASWATHI S" refreshedDate="46269.924184722222" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="5" xr:uid="{AEDF05A9-47DE-4A83-91C9-2FE8E56531AD}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F6" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="S.NO" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="DATE" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-09-04T00:00:00" maxDate="2026-09-09T00:00:00"/>
+    </cacheField>
+    <cacheField name="NAME" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Priya"/>
+        <s v="Raja"/>
+        <s v="Sasi"/>
+        <s v="Mani"/>
+        <s v="Saras"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="DEPARTMENT" numFmtId="0">
+      <sharedItems count="3">
+        <s v="IT"/>
+        <s v="FINANCE"/>
+        <s v="HR"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="SALARY" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="25000" maxValue="35000"/>
+    </cacheField>
+    <cacheField name="CATEGORY" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="5">
+  <r>
+    <n v="5"/>
+    <d v="2026-09-08T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="35000"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <d v="2026-09-06T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="32000"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <d v="2026-09-07T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="30000"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <d v="2026-09-05T00:00:00"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="28000"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <d v="2026-09-04T00:00:00"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="25000"/>
+    <s v="Low"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{376F9CC2-D9D6-444F-BA09-F8CF7905756C}" name="PivotTable4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of NAME" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -533,8 +3071,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDB242A-726F-486D-9C8E-C6FBAF899A46}">
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="8">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1216218D-7164-4BB7-AF76-327B0BB54A14}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -542,10 +3134,12 @@
     <col min="3" max="3" width="16.109375" customWidth="1"/>
     <col min="4" max="4" width="22.77734375" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" customWidth="1"/>
-    <col min="7" max="7" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="11" max="11" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,14 +3158,17 @@
       <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -591,8 +3188,15 @@
         <f>IF(E2&gt;=30000,"High","Low")</f>
         <v>High</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="2">
+        <f>AVERAGE(E2:E6)</f>
+        <v>30000</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -612,15 +3216,22 @@
         <f>IF(E3&gt;=30000,"High","Low")</f>
         <v>High</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <f>COUNTIFS(D1:D6,"IT",E1:E6,"&gt;=30000")</f>
         <v>2</v>
       </c>
+      <c r="K3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNT(E2:E6)</f>
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -640,15 +3251,22 @@
         <f>IF(E4&gt;=30000,"High","Low")</f>
         <v>High</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <f>SUMIFS(E1:E6,D1:D6,"IT",E1:E6,"&gt;=30000")</f>
         <v>67000</v>
       </c>
+      <c r="K4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="2">
+        <f>SUM(E2:E6)</f>
+        <v>150000</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -668,15 +3286,22 @@
         <f>IF(E5&gt;=30000,"High","Low")</f>
         <v>Low</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <f>SUMIF(D2:D6,"IT",E2:E6)</f>
         <v>92000</v>
       </c>
+      <c r="K5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="2">
+        <f>MAX(E2:E6)</f>
+        <v>35000</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -696,59 +3321,17 @@
         <f>IF(E6&gt;=30000,"High","Low")</f>
         <v>Low</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f>COUNTIF(F2:F6,"High")</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2">
-        <f>AVERAGE(E2:E6)</f>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2">
-        <f>COUNT(E2:E6)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2">
-        <f>SUM(E2:E6)</f>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2">
-        <f>MAX(E2:E6)</f>
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D12" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="2">
+      <c r="L6" s="2">
         <f>MIN(E2:E6)</f>
         <v>25000</v>
       </c>
@@ -761,16 +3344,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467A3BE6-9EBD-45ED-881F-F2E70BB7CADC}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="1" max="1" width="62.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="3"/>
@@ -832,5 +3415,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>